--- a/backend/enquiry.xlsx
+++ b/backend/enquiry.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:H2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -410,7 +410,19 @@
         <v>Email</v>
       </c>
       <c r="D1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="E1" t="str">
+        <v>ProjectType</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Timeline</v>
+      </c>
+      <c r="G1" t="str">
         <v>Message</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Date</v>
       </c>
     </row>
     <row r="2">
@@ -424,12 +436,24 @@
         <v>ismat@gmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>abvcd</v>
+        <v>zylow</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Web App</v>
+      </c>
+      <c r="F2" t="str">
+        <v>1 Month</v>
+      </c>
+      <c r="G2" t="str">
+        <v>efghi</v>
+      </c>
+      <c r="H2" t="str">
+        <v>5/1/2026, 2:29:52 PM</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/enquiry.xlsx
+++ b/backend/enquiry.xlsx
@@ -427,28 +427,28 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Ismat</v>
+        <v>ismat</v>
       </c>
       <c r="B2" t="str">
-        <v>8888888888</v>
+        <v>9999999999</v>
       </c>
       <c r="C2" t="str">
         <v>ismat@gmail.com</v>
       </c>
       <c r="D2" t="str">
-        <v>zylow</v>
+        <v/>
       </c>
       <c r="E2" t="str">
-        <v>Web App</v>
+        <v>Website</v>
       </c>
       <c r="F2" t="str">
-        <v>1 Month</v>
+        <v>Later</v>
       </c>
       <c r="G2" t="str">
-        <v>efghi</v>
+        <v>abc</v>
       </c>
       <c r="H2" t="str">
-        <v>5/1/2026, 2:29:52 PM</v>
+        <v>6/12/2026, 11:04:13 AM</v>
       </c>
     </row>
   </sheetData>
